--- a/gbs-location-selection.xlsx
+++ b/gbs-location-selection.xlsx
@@ -652,7 +652,7 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>•  Six established locations are absent because the postings feed does not reach them: Manila, Kuala Lumpur, Bucharest, Prague, Budapest and Lisbon. The ranking is therefore within the cities shown, not against every credible alternative.</t>
+          <t>•  Six established locations sit outside the ranking because the postings feed does not reach them: Manila, Kuala Lumpur, Bucharest, Prague, Budapest and Lisbon. Five pillars do reach them and are reported under 'Beyond the sample'; capability and employer depth are the two that cannot be, so these markets are never scored against the ranked cities.</t>
         </is>
       </c>
     </row>

--- a/gbs-location-selection.xlsx
+++ b/gbs-location-selection.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Criteria &amp; weights" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="City ranking" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Wage gap" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Not ranked" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="8">
     <font>
       <name val="Calibri"/>
@@ -104,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -150,6 +153,18 @@
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
@@ -3522,4 +3537,388 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>GBS &amp; GCC LOCATION SELECTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Locations outside the ranking</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Five pillars reach these markets because ILOSTAT and the World Bank cover every country alike. Capability and employer depth do not, and those are the two the job postings carry, so nothing here is scored or ranked against the cities that are.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Cost USD / month</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Observed</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>Relevant workforce</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Hours shared with HQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Prague</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Czechia</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="n">
+        <v>3127.649739729742</v>
+      </c>
+      <c r="D6" s="19" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>2352383</v>
+      </c>
+      <c r="F6" s="19" t="n">
+        <v>75.02690106</v>
+      </c>
+      <c r="G6" s="20" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="n">
+        <v>2205.205546047026</v>
+      </c>
+      <c r="D7" s="21" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E7" s="18" t="n">
+        <v>2346761</v>
+      </c>
+      <c r="F7" s="21" t="n">
+        <v>60.14429548</v>
+      </c>
+      <c r="G7" s="22" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>San José</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Costa Rica</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="n">
+        <v>1658.844198230243</v>
+      </c>
+      <c r="D8" s="19" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>722616</v>
+      </c>
+      <c r="F8" s="19" t="n">
+        <v>67.2234613</v>
+      </c>
+      <c r="G8" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="n">
+        <v>1622.446997552137</v>
+      </c>
+      <c r="D9" s="21" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E9" s="18" t="n">
+        <v>2205427</v>
+      </c>
+      <c r="F9" s="21" t="n">
+        <v>70.26399764</v>
+      </c>
+      <c r="G9" s="22" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Budapest</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="n">
+        <v>1452.993599350319</v>
+      </c>
+      <c r="D10" s="19" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>2170460</v>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>60.70442944</v>
+      </c>
+      <c r="G10" s="20" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="n">
+        <v>904.4593513387189</v>
+      </c>
+      <c r="D11" s="21" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>5647196</v>
+      </c>
+      <c r="F11" s="21" t="n">
+        <v>65.60742774000001</v>
+      </c>
+      <c r="G11" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="n">
+        <v>716.7530708855829</v>
+      </c>
+      <c r="D12" s="19" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>5959091</v>
+      </c>
+      <c r="F12" s="19" t="n">
+        <v>48.56104388</v>
+      </c>
+      <c r="G12" s="20" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>Santo Domingo</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="n">
+        <v>645.8720670166648</v>
+      </c>
+      <c r="D13" s="21" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>1272228</v>
+      </c>
+      <c r="F13" s="21" t="n">
+        <v>56.63891526</v>
+      </c>
+      <c r="G13" s="22" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>Manila</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="n">
+        <v>505.3461322199106</v>
+      </c>
+      <c r="D14" s="19" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>9208417</v>
+      </c>
+      <c r="F14" s="19" t="n">
+        <v>49.2408423</v>
+      </c>
+      <c r="G14" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Ho Chi Minh City</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="n">
+        <v>478.1951984488104</v>
+      </c>
+      <c r="D15" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>7277217</v>
+      </c>
+      <c r="F15" s="21" t="n">
+        <v>52.10275567999999</v>
+      </c>
+      <c r="G15" s="22" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Three other kinds of absence</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Seen but too thin: 105 locations appear in the sample and clear neither threshold. Closest are Gdańsk (7 postings, 3 employers), Katowice (7 postings, 3 employers), Delhi (6 postings, 3 employers), Łódź (4 postings, 3 employers). The employer count is usually what stops them, and one employer hiring is an office rather than a centre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Not priceable: China (Wuxi, Dalian, Chengdu) and Morocco (Casablanca, Rabat). ILOSTAT publishes no earnings by occupation for either, so there is no cost figure on the basis every market here uses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Incoherent: Egypt reports professionals at 1.06x clerical pay against 1.3-2.9x in every other market, so it is excluded by test rather than by judgement.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A18:G18"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/gbs-location-selection.xlsx
+++ b/gbs-location-selection.xlsx
@@ -532,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="104" customWidth="1" min="1" max="1"/>
@@ -653,26 +653,33 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>•  Exhibit 3 subtracts a national baseline from cities that sometimes carry a regional index, so a capital-city premium sits on one side of it and not the other. Warsaw against a UK baseline is the clearest case: it reads as dearer than the UK, which is partly Mazowieckie against a British national mean rather than a wage fact.</t>
+          <t>•  A second job board would not close the coverage gap. Employer depth counts distinct employers within one feed, so another feed’s count is not comparable, and splicing one in would move Manila into the ranking on evidence unlike the rest.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>•  Exhibit 3 is a wage line, not a business case. It excludes facilities, technology, management overhead, transition and severance, and holds headcount one-for-one. Read it as the upper bound on one component of the saving.</t>
+          <t>•  Exhibit 3 subtracts a national baseline from cities that sometimes carry a regional index, so a capital-city premium sits on one side of it and not the other. Warsaw against a UK baseline is the clearest case: it reads as dearer than the UK, which is partly Mazowieckie against a British national mean rather than a wage fact.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
+          <t>•  Exhibit 3 is a wage line, not a business case. It excludes facilities, technology, management overhead, transition and severance, and holds headcount one-for-one. Read it as the upper bound on one component of the saving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
           <t>•  Six established locations sit outside the ranking because the postings feed does not reach them: Manila, Kuala Lumpur, Bucharest, Prague, Budapest and Lisbon. Five pillars do reach them and are reported under 'Beyond the sample'; capability and employer depth are the two that cannot be, so these markets are never scored against the ranked cities.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>Postings sample: August 2026.  Method and code: github.com/morichtereur/gbs-location-selection</t>
         </is>

--- a/gbs-location-selection.xlsx
+++ b/gbs-location-selection.xlsx
@@ -532,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="104" customWidth="1" min="1" max="1"/>
@@ -646,42 +646,35 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>•  One snapshot. A city hiring quietly during the fetch is under-represented; absence is weak evidence, not a verdict.</t>
+          <t>•  A second job board would not close the coverage gap. Employer depth counts distinct employers within one feed, so another feed’s count is not comparable, and splicing one in would move Manila into the ranking on evidence unlike the rest.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>•  A second job board would not close the coverage gap. Employer depth counts distinct employers within one feed, so another feed’s count is not comparable, and splicing one in would move Manila into the ranking on evidence unlike the rest.</t>
+          <t>•  Exhibit 3 subtracts a national baseline from cities that sometimes carry a regional index, so a capital-city premium sits on one side of it and not the other. Warsaw against a UK baseline is the clearest case: it reads as dearer than the UK, which is partly Mazowieckie against a British national mean rather than a wage fact.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>•  Exhibit 3 subtracts a national baseline from cities that sometimes carry a regional index, so a capital-city premium sits on one side of it and not the other. Warsaw against a UK baseline is the clearest case: it reads as dearer than the UK, which is partly Mazowieckie against a British national mean rather than a wage fact.</t>
+          <t>•  Exhibit 3 is a wage line, not a business case. It excludes facilities, technology, management overhead, transition and severance, and holds headcount one-for-one. Read it as the upper bound on one component of the saving.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>•  Exhibit 3 is a wage line, not a business case. It excludes facilities, technology, management overhead, transition and severance, and holds headcount one-for-one. Read it as the upper bound on one component of the saving.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
           <t>•  Six established locations sit outside the ranking because the postings feed does not reach them: Manila, Kuala Lumpur, Bucharest, Prague, Budapest and Lisbon. Five pillars do reach them and are reported under 'Beyond the sample'; capability and employer depth are the two that cannot be, so these markets are never scored against the ranked cities.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Postings sample: August 2026.  Method and code: github.com/morichtereur/gbs-location-selection</t>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Postings sample: 22 August 2026.  Method and code: github.com/morichtereur/gbs-location-selection</t>
         </is>
       </c>
     </row>
@@ -787,11 +780,7 @@
           <t>ILOSTAT earnings by occupation</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>2020–2025</t>
-        </is>
-      </c>
+      <c r="E6" s="9" t="n"/>
       <c r="F6" s="10" t="n">
         <v>0.3</v>
       </c>
@@ -820,11 +809,7 @@
           <t>ILOSTAT employment by occupation</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
+      <c r="E7" s="11" t="n"/>
       <c r="F7" s="12" t="n">
         <v>0.18</v>
       </c>
@@ -853,11 +838,7 @@
           <t>World Bank Worldwide Governance Indicators</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
+      <c r="E8" s="9" t="n"/>
       <c r="F8" s="10" t="n">
         <v>0.09</v>
       </c>
@@ -886,11 +867,7 @@
           <t>Adzuna job postings</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>Aug 2026</t>
-        </is>
-      </c>
+      <c r="E9" s="11" t="n"/>
       <c r="F9" s="12" t="n">
         <v>0.13</v>
       </c>
@@ -952,11 +929,7 @@
           <t>ILOSTAT, derived</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>2015–2025</t>
-        </is>
-      </c>
+      <c r="E11" s="11" t="n"/>
       <c r="F11" s="12" t="n">
         <v>0.09</v>
       </c>
@@ -985,11 +958,7 @@
           <t>Adzuna job postings</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>Aug 2026</t>
-        </is>
-      </c>
+      <c r="E12" s="9" t="n"/>
       <c r="F12" s="10" t="n">
         <v>0.12</v>
       </c>
@@ -2368,14 +2337,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S39"/>
+  <dimension ref="A1:S58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
@@ -3521,21 +3490,314 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>A positive figure is the annual wage the move takes out per role; a negative one means the city is dearer than the origin.</t>
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Fully loaded, against the default origin</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>The origin is always a national figure while the Polish cities carry a regional index, so a capital-city premium sits on one side of the subtraction and not the other.</t>
+          <t>Employer loading 25% of gross wage, applied to origin and destination alike. Attrition backfill 15%, applied to the destination only, since the origin is not being stood up. Projection horizon 0 years, at each market's own measured wage drift.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>The first two are assumptions, not measurements. No free source gives comparable employer-charge schedules for all eleven markets, so the factor is uniform — which scales every gap and cannot reorder them. Real charges differ sharply by country, and pricing that difference is exactly what this study cannot do. Change the numbers in src/config.py to re-run on your own. Origin: Switzerland.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="26" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>Loaded cost USD / month</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>Base gap vs Switzerland</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>Loaded gap vs Switzerland</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>City-level wage?</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>Warsaw</t>
+        </is>
+      </c>
+      <c r="B42" s="16" t="n">
+        <v>6789.216886855975</v>
+      </c>
+      <c r="C42" s="16" t="n">
+        <v>42744.17687174902</v>
+      </c>
+      <c r="D42" s="16" t="n">
+        <v>42803.62074504215</v>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>Kraków</t>
+        </is>
+      </c>
+      <c r="B43" s="18" t="n">
+        <v>5478.102168209887</v>
+      </c>
+      <c r="C43" s="18" t="n">
+        <v>53689.13452305548</v>
+      </c>
+      <c r="D43" s="18" t="n">
+        <v>58536.9973687952</v>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>Wrocław</t>
+        </is>
+      </c>
+      <c r="B44" s="16" t="n">
+        <v>4260.923559942105</v>
+      </c>
+      <c r="C44" s="16" t="n">
+        <v>63849.92986163872</v>
+      </c>
+      <c r="D44" s="16" t="n">
+        <v>73143.14066800858</v>
+      </c>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>Poznań</t>
+        </is>
+      </c>
+      <c r="B45" s="18" t="n">
+        <v>3261.88371955932</v>
+      </c>
+      <c r="C45" s="18" t="n">
+        <v>72189.74070309501</v>
+      </c>
+      <c r="D45" s="18" t="n">
+        <v>85131.61875260199</v>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>Johannesburg</t>
+        </is>
+      </c>
+      <c r="B46" s="16" t="n">
+        <v>1227.73778350239</v>
+      </c>
+      <c r="C46" s="16" t="n">
+        <v>89170.43721278764</v>
+      </c>
+      <c r="D46" s="16" t="n">
+        <v>109541.3699852852</v>
+      </c>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>national wage</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="B47" s="18" t="n">
+        <v>1202.385660718941</v>
+      </c>
+      <c r="C47" s="18" t="n">
+        <v>89382.07232471905</v>
+      </c>
+      <c r="D47" s="18" t="n">
+        <v>109845.5954586866</v>
+      </c>
+      <c r="E47" s="11" t="inlineStr">
+        <is>
+          <t>national wage</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="B48" s="16" t="n">
+        <v>491.6612147170598</v>
+      </c>
+      <c r="C48" s="16" t="n">
+        <v>95315.07639569127</v>
+      </c>
+      <c r="D48" s="16" t="n">
+        <v>118374.2888107091</v>
+      </c>
+      <c r="E48" s="9" t="inlineStr">
+        <is>
+          <t>national wage</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+      <c r="B49" s="18" t="n">
+        <v>491.6612147170598</v>
+      </c>
+      <c r="C49" s="18" t="n">
+        <v>95315.07639569127</v>
+      </c>
+      <c r="D49" s="18" t="n">
+        <v>118374.2888107091</v>
+      </c>
+      <c r="E49" s="11" t="inlineStr">
+        <is>
+          <t>national wage</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="B50" s="16" t="n">
+        <v>491.6612147170598</v>
+      </c>
+      <c r="C50" s="16" t="n">
+        <v>95315.07639569127</v>
+      </c>
+      <c r="D50" s="16" t="n">
+        <v>118374.2888107091</v>
+      </c>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>national wage</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="B51" s="18" t="n">
+        <v>491.6612147170598</v>
+      </c>
+      <c r="C51" s="18" t="n">
+        <v>95315.07639569127</v>
+      </c>
+      <c r="D51" s="18" t="n">
+        <v>118374.2888107091</v>
+      </c>
+      <c r="E51" s="11" t="inlineStr">
+        <is>
+          <t>national wage</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="B52" s="16" t="n">
+        <v>491.6612147170598</v>
+      </c>
+      <c r="C52" s="16" t="n">
+        <v>95315.07639569127</v>
+      </c>
+      <c r="D52" s="16" t="n">
+        <v>118374.2888107091</v>
+      </c>
+      <c r="E52" s="9" t="inlineStr">
+        <is>
+          <t>national wage</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>A positive figure is the annual wage the move takes out per role; a negative one means the city is dearer than the origin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>The grid above is the gross wage line. The loaded figures are in the block beneath it, and are not a fixed multiple of the grid: the attrition uplift applies to the destination only, so it moves cheap and dear cities by different amounts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>The origin is always a national figure while the Polish cities carry a regional index, so a capital-city premium sits on one side of the subtraction and not the other.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>A city marked 'national wage' has no city-level earnings in any reachable source, so neither side of its gap carries a city premium.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>Germany's earnings come from EU-SILC where the others come from labour force surveys, and Germany (2022) and Singapore (2021) are the oldest observations in the set.</t>
         </is>
